--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC95BB73-1746-464D-96BF-47355155B863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D375121-91E8-4431-B2B1-C1F10B74ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,52 +42,52 @@
     <t>UG TRB</t>
   </si>
   <si>
-    <t>Ayyanar</t>
-  </si>
-  <si>
-    <t>26ayyan482</t>
-  </si>
-  <si>
-    <t>KSayPG@739</t>
-  </si>
-  <si>
-    <t>perumal raj</t>
-  </si>
-  <si>
-    <t>26perum615</t>
-  </si>
-  <si>
-    <t>KSpePG#084</t>
-  </si>
-  <si>
     <t>PG TRB</t>
   </si>
   <si>
-    <t>Suba Annamalai</t>
-  </si>
-  <si>
-    <t>26subaa482</t>
-  </si>
-  <si>
-    <t>KSsuUG@700</t>
-  </si>
-  <si>
-    <t>Sheelajegan</t>
-  </si>
-  <si>
-    <t>26sheela615</t>
-  </si>
-  <si>
-    <t>KSshUG#180</t>
-  </si>
-  <si>
-    <t>Ranjitham R</t>
-  </si>
-  <si>
-    <t>26ranji903</t>
-  </si>
-  <si>
-    <t>KSraUG*517</t>
+    <t>R. Malarvizhi</t>
+  </si>
+  <si>
+    <t>Sivasankari</t>
+  </si>
+  <si>
+    <t>26malar482</t>
+  </si>
+  <si>
+    <t>KSmaUG@7939</t>
+  </si>
+  <si>
+    <t>26sivas615</t>
+  </si>
+  <si>
+    <t>KSsiUG#2584</t>
+  </si>
+  <si>
+    <t>Tharma Sheela</t>
+  </si>
+  <si>
+    <t>26tharm482</t>
+  </si>
+  <si>
+    <t>KSthPG@7309</t>
+  </si>
+  <si>
+    <t>Janani S M</t>
+  </si>
+  <si>
+    <t>26janan615</t>
+  </si>
+  <si>
+    <t>KSjaPG#2840</t>
+  </si>
+  <si>
+    <t>Bhuvaneswari N</t>
+  </si>
+  <si>
+    <t>26bhuva903</t>
+  </si>
+  <si>
+    <t>KSbhPG*5216</t>
   </si>
 </sst>
 </file>
@@ -98,13 +98,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -131,10 +124,14 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00ADE7"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Nunito Sans"/>
     </font>
   </fonts>
   <fills count="3">
@@ -190,21 +187,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -486,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -508,36 +506,36 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -546,12 +544,12 @@
       <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -560,12 +558,12 @@
       <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>4</v>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -574,26 +572,14 @@
       <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{30E7388B-44DE-487D-BC07-75261574273C}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{D22CEE41-69E7-4B77-BC1B-9857D1C1B28D}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{28D54052-0F81-48E9-A14E-92C3ACBAC5A4}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{8E0CFF5E-69C3-4555-8469-0AC4D3902B21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D375121-91E8-4431-B2B1-C1F10B74ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B043446-0E95-43D6-B5BE-FBE2B74DAA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>name</t>
   </si>
@@ -42,9 +42,6 @@
     <t>UG TRB</t>
   </si>
   <si>
-    <t>PG TRB</t>
-  </si>
-  <si>
     <t>R. Malarvizhi</t>
   </si>
   <si>
@@ -54,47 +51,38 @@
     <t>26malar482</t>
   </si>
   <si>
-    <t>KSmaUG@7939</t>
-  </si>
-  <si>
     <t>26sivas615</t>
   </si>
   <si>
-    <t>KSsiUG#2584</t>
-  </si>
-  <si>
-    <t>Tharma Sheela</t>
-  </si>
-  <si>
-    <t>26tharm482</t>
-  </si>
-  <si>
-    <t>KSthPG@7309</t>
-  </si>
-  <si>
-    <t>Janani S M</t>
-  </si>
-  <si>
-    <t>26janan615</t>
-  </si>
-  <si>
-    <t>KSjaPG#2840</t>
-  </si>
-  <si>
-    <t>Bhuvaneswari N</t>
-  </si>
-  <si>
-    <t>26bhuva903</t>
-  </si>
-  <si>
-    <t>KSbhPG*5216</t>
+    <t>KSmaUG@7309</t>
+  </si>
+  <si>
+    <t>KSsiUG#2814</t>
+  </si>
+  <si>
+    <t>Kanakaraj M</t>
+  </si>
+  <si>
+    <t>26kanak903</t>
+  </si>
+  <si>
+    <t>KSkaUG*5167</t>
+  </si>
+  <si>
+    <t>P. Punitha</t>
+  </si>
+  <si>
+    <t>26punit472</t>
+  </si>
+  <si>
+    <t>KSpuUG@6380</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,26 +117,16 @@
       <color rgb="FF00ADE7"/>
       <name val="Nunito Sans"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Nunito Sans"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -171,30 +149,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -202,7 +165,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -484,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -499,7 +461,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -507,79 +469,65 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>5</v>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{28D54052-0F81-48E9-A14E-92C3ACBAC5A4}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{8E0CFF5E-69C3-4555-8469-0AC4D3902B21}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{246A1EB8-F9C6-4356-A867-568E8F2911CB}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{ABA36234-5885-4086-AA84-58FC255AEBE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B043446-0E95-43D6-B5BE-FBE2B74DAA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E5E51A-EC72-4998-B849-DC99FDE9D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>name</t>
   </si>
@@ -39,50 +39,41 @@
     <t>category</t>
   </si>
   <si>
-    <t>UG TRB</t>
-  </si>
-  <si>
-    <t>R. Malarvizhi</t>
-  </si>
-  <si>
-    <t>Sivasankari</t>
-  </si>
-  <si>
-    <t>26malar482</t>
-  </si>
-  <si>
-    <t>26sivas615</t>
-  </si>
-  <si>
-    <t>KSmaUG@7309</t>
-  </si>
-  <si>
-    <t>KSsiUG#2814</t>
-  </si>
-  <si>
-    <t>Kanakaraj M</t>
-  </si>
-  <si>
-    <t>26kanak903</t>
-  </si>
-  <si>
-    <t>KSkaUG*5167</t>
-  </si>
-  <si>
-    <t>P. Punitha</t>
-  </si>
-  <si>
-    <t>26punit472</t>
-  </si>
-  <si>
-    <t>KSpuUG@6380</t>
+    <t>Jeyabarathi M</t>
+  </si>
+  <si>
+    <t>26jeyab482</t>
+  </si>
+  <si>
+    <t>KSjeUG@739</t>
+  </si>
+  <si>
+    <t>Govindarasu</t>
+  </si>
+  <si>
+    <t>26govin615</t>
+  </si>
+  <si>
+    <t>KSgoUG#284</t>
+  </si>
+  <si>
+    <t>VINAYAGAM</t>
+  </si>
+  <si>
+    <t>26vinay903</t>
+  </si>
+  <si>
+    <t>KSviUG*516</t>
+  </si>
+  <si>
+    <t>PG TRB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,14 +85,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -150,24 +133,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -446,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -469,66 +447,48 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
+      <c r="A3" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{246A1EB8-F9C6-4356-A867-568E8F2911CB}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{ABA36234-5885-4086-AA84-58FC255AEBE0}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E5E51A-EC72-4998-B849-DC99FDE9D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D17C6-D827-4F86-BC16-60597035A774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,35 +45,35 @@
     <t>26jeyab482</t>
   </si>
   <si>
-    <t>KSjeUG@739</t>
-  </si>
-  <si>
     <t>Govindarasu</t>
   </si>
   <si>
     <t>26govin615</t>
   </si>
   <si>
-    <t>KSgoUG#284</t>
-  </si>
-  <si>
     <t>VINAYAGAM</t>
   </si>
   <si>
     <t>26vinay903</t>
   </si>
   <si>
-    <t>KSviUG*516</t>
-  </si>
-  <si>
     <t>PG TRB</t>
+  </si>
+  <si>
+    <t>KSjePG@739</t>
+  </si>
+  <si>
+    <t>KSgoPG#284</t>
+  </si>
+  <si>
+    <t>KSviPG*516</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +90,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -101,12 +109,18 @@
       <name val="Nunito Sans"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -133,19 +147,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -447,48 +467,51 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B108F7F5-45E3-4846-90E1-368C35D10241}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896D17C6-D827-4F86-BC16-60597035A774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7CFDB7-0E7D-41DB-98BB-D6227CB2FC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>name</t>
   </si>
@@ -39,41 +39,53 @@
     <t>category</t>
   </si>
   <si>
-    <t>Jeyabarathi M</t>
-  </si>
-  <si>
-    <t>26jeyab482</t>
-  </si>
-  <si>
-    <t>Govindarasu</t>
-  </si>
-  <si>
-    <t>26govin615</t>
-  </si>
-  <si>
-    <t>VINAYAGAM</t>
-  </si>
-  <si>
-    <t>26vinay903</t>
+    <t>UG TRB</t>
+  </si>
+  <si>
+    <t>Sangeetha</t>
+  </si>
+  <si>
+    <t>26sange482</t>
+  </si>
+  <si>
+    <t>KSsaPG@2739</t>
+  </si>
+  <si>
+    <t>Yazhini</t>
+  </si>
+  <si>
+    <t>26yazhi615</t>
+  </si>
+  <si>
+    <t>KSyaPG#2834</t>
   </si>
   <si>
     <t>PG TRB</t>
   </si>
   <si>
-    <t>KSjePG@739</t>
-  </si>
-  <si>
-    <t>KSgoPG#284</t>
-  </si>
-  <si>
-    <t>KSviPG*516</t>
+    <t>Maria Therese</t>
+  </si>
+  <si>
+    <t>26maria903</t>
+  </si>
+  <si>
+    <t>KSmaUG*5016</t>
+  </si>
+  <si>
+    <t>kalai mathi</t>
+  </si>
+  <si>
+    <t>26kalai472</t>
+  </si>
+  <si>
+    <t>KSkaUG@6328</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +102,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00ADE7"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -98,29 +123,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF00ADE7"/>
+      <sz val="8"/>
+      <color rgb="FF7D8592"/>
       <name val="Nunito Sans"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -149,20 +162,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -444,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -466,51 +479,66 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{B108F7F5-45E3-4846-90E1-368C35D10241}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{DEB66525-EF19-43E0-B97F-6571BA8EA49C}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{A0F84F5A-A0BC-4EB4-BB7D-9236E7E4EBB7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7CFDB7-0E7D-41DB-98BB-D6227CB2FC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A136F7B-A5FB-4DC3-B57D-066AD267A3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45120" yWindow="-2175" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>name</t>
   </si>
@@ -39,46 +39,25 @@
     <t>category</t>
   </si>
   <si>
-    <t>UG TRB</t>
-  </si>
-  <si>
     <t>Sangeetha</t>
   </si>
   <si>
-    <t>26sange482</t>
-  </si>
-  <si>
-    <t>KSsaPG@2739</t>
-  </si>
-  <si>
     <t>Yazhini</t>
   </si>
   <si>
-    <t>26yazhi615</t>
-  </si>
-  <si>
-    <t>KSyaPG#2834</t>
-  </si>
-  <si>
     <t>PG TRB</t>
   </si>
   <si>
-    <t>Maria Therese</t>
-  </si>
-  <si>
-    <t>26maria903</t>
-  </si>
-  <si>
-    <t>KSmaUG*5016</t>
-  </si>
-  <si>
-    <t>kalai mathi</t>
-  </si>
-  <si>
-    <t>26kalai472</t>
-  </si>
-  <si>
-    <t>KSkaUG@6328</t>
+    <t>26sangg482</t>
+  </si>
+  <si>
+    <t>KS12PG*2739</t>
+  </si>
+  <si>
+    <t>26yaazz615</t>
+  </si>
+  <si>
+    <t>KSyaaPG#2834</t>
   </si>
 </sst>
 </file>
@@ -481,21 +460,21 @@
     </row>
     <row r="2" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
@@ -504,41 +483,24 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{DEB66525-EF19-43E0-B97F-6571BA8EA49C}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{A0F84F5A-A0BC-4EB4-BB7D-9236E7E4EBB7}"/>
+    <hyperlink ref="C2" r:id="rId1" display="KSsaPG@2739" xr:uid="{DEB66525-EF19-43E0-B97F-6571BA8EA49C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A136F7B-A5FB-4DC3-B57D-066AD267A3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEE07B4-407C-488D-A754-953D19F209B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45120" yWindow="-2175" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,32 +39,32 @@
     <t>category</t>
   </si>
   <si>
-    <t>Sangeetha</t>
-  </si>
-  <si>
-    <t>Yazhini</t>
-  </si>
-  <si>
     <t>PG TRB</t>
   </si>
   <si>
-    <t>26sangg482</t>
-  </si>
-  <si>
-    <t>KS12PG*2739</t>
-  </si>
-  <si>
-    <t>26yaazz615</t>
-  </si>
-  <si>
-    <t>KSyaaPG#2834</t>
+    <t>Merline Betsy</t>
+  </si>
+  <si>
+    <t>26etsy1016</t>
+  </si>
+  <si>
+    <t>KSneePG#2835</t>
+  </si>
+  <si>
+    <t>Nagarajan .A</t>
+  </si>
+  <si>
+    <t>26rajan1017</t>
+  </si>
+  <si>
+    <t>KSjaaPG#2816</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,26 +93,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF7D8592"/>
-      <name val="Nunito Sans"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -139,25 +132,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -436,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -458,50 +444,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="KSsaPG@2739" xr:uid="{DEB66525-EF19-43E0-B97F-6571BA8EA49C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/uploads/USER_ID.xlsx
+++ b/uploads/USER_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthi K\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEE07B4-407C-488D-A754-953D19F209B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B25E9BB-924E-450D-B941-D547BE808B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>name</t>
   </si>
@@ -42,29 +42,38 @@
     <t>PG TRB</t>
   </si>
   <si>
-    <t>Merline Betsy</t>
-  </si>
-  <si>
-    <t>26etsy1016</t>
-  </si>
-  <si>
-    <t>KSneePG#2835</t>
-  </si>
-  <si>
-    <t>Nagarajan .A</t>
-  </si>
-  <si>
-    <t>26rajan1017</t>
-  </si>
-  <si>
-    <t>KSjaaPG#2816</t>
+    <t>Jeeva</t>
+  </si>
+  <si>
+    <t>26jeevaa482</t>
+  </si>
+  <si>
+    <t>KSjePG@7390</t>
+  </si>
+  <si>
+    <t>Saranya Natarajan</t>
+  </si>
+  <si>
+    <t>26sarann615</t>
+  </si>
+  <si>
+    <t>KSsaPG#2184</t>
+  </si>
+  <si>
+    <t>Kovalan D</t>
+  </si>
+  <si>
+    <t>26kovaal903</t>
+  </si>
+  <si>
+    <t>KSkoPG*5165</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,31 +90,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF00ADE7"/>
-      <name val="Nunito Sans"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Nunito Sans"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,18 +143,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -422,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" customWidth="1"/>
@@ -444,11 +461,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -462,17 +479,34 @@
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="4" spans="1:4" ht="16.8" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{EA9BB217-25C7-4341-915E-8785DA9D397B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>